--- a/data/worldcup_0625_0622update.xlsx
+++ b/data/worldcup_0625_0622update.xlsx
@@ -7,10 +7,12 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="瑞士vs加拿大" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="苏格兰vs巴西" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="摩洛哥vs海地" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="苏格兰vs巴西" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="捷克vs墨西哥" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="瑞士vs加拿大" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="波黑vs卡塔尔" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="捷克vs墨西哥" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="南非vs韩国" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -420,7 +422,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E19"/>
+  <dimension ref="A1:E49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="60" customWidth="1" min="1" max="1"/>
@@ -458,423 +460,435 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>官方：巴西裁判阿巴蒂将执法世界杯瑞士vs加拿大</t>
+          <t>Neymar completes first World Cup training session before Brazil vs. Scotland</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>dongqiudi_team</t>
+          <t>espn_pw</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2026-06-21 20:48</t>
+          <t>2026-06-22T08:40:32</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>https://www.dongqiudi.com/articles/5955280.html</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr"/>
+          <t>https://www.espn.com/soccer/story/_/id/49142107/neymar-completes-first-world-cup-training-session-brazil-vs-scotland</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Neymar completed his first full training session with Brazil on Sunday.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>World Cup 2026 news and live updates - USA, Canada and Mexico latest including Trump, tickets and fans</t>
+          <t>Lucas Paqueta: Brazil have 'great respect' for Scotland</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>skysports</t>
+          <t>espn_pw</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Sun, 21 Jun 2026 15</t>
+          <t>2026-06-21T23:39:02</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>https://www.skysports.com/football/live-blog/12040/13509050/world-cup-2026-news-and-live-updates-usa-canada-and-mexico-latest-including-trump-tickets-and-fans</t>
+          <t>https://www.espn.com/soccer/story/_/id/49138795/lucas-paqueta-brazil-scotland-fifa-world-cup-2026</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Update World Cup 2026 news and live updates - USA, Canada and Mexico latest including Trump, tickets and fans Sunday 21 June 2026 15:14, UK Sorry, thi</t>
+          <t>Brazil playmaker Lucas Paquetá says he has "great respect" for Scotland ahead of the decisive clash between the teams in Miami on Wednesday.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>The 2026 World Cup team of the tournament so far (without the superstars)</t>
+          <t>官方：墨西哥裁判拉莫斯将执法世界杯苏格兰vs巴西</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>guardian</t>
+          <t>dongqiudi_team</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Sun, 21 Jun 2026 04</t>
+          <t>2026-06-21 20:39</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>https://www.theguardian.com/football/2026/jun/21/the-2026-world-cup-team-of-the-tournament-so-far-without-the-superstars</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>We pick an XI of players who have impressed during the initial rounds of games in Canada, the US and Mexico  A star was born, at 40, when a player who</t>
-        </is>
-      </c>
+          <t>https://www.dongqiudi.com/articles/5955264.html</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>How to watch Germany vs Ivory Coast for FREE: Live stream details &amp; TV channels for World Cup 2026 as Kai Havertz tries to add to tally</t>
+          <t>苏格兰主帅：对摩洛哥我们踢得有点慢热；末轮要死磕巴西</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>fourfourtwo</t>
+          <t>dongqiudi_team</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Sat, 20 Jun 2026 18</t>
+          <t>2026-06-21 00:26</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>https://www.fourfourtwo.com/competition/watch-germany-vs-ivory-coast-free-world-cup-2026</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>Germany and the Ivory Coast may have won their respective opening games at the World Cup 2026 , but the contrasting manner in which they each delivere</t>
-        </is>
-      </c>
+          <t>https://www.dongqiudi.com/articles/5953238.html</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Today's World Cup 2026 Kickoff Times: Complete Pacific Time (PT) Schedule</t>
+          <t>Guns for hire and gegenpress eggheads bring World Cup subplots aplenty</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>goal_pw</t>
+          <t>guardian</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2026-06-21T17:04:43</t>
+          <t>Sun, 21 Jun 2026 13</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>https://www.goal.com/en/news/world-cup-2026-pacific-time-schedule/blt708391eb6f8f1517</t>
+          <t>https://www.theguardian.com/football/2026/jun/21/football-daily-geopolitics-world-cup-maverick-managerial-matchups</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>An all-you-need-to-know guide on how to watch every World Cup game broadcast live in the Pacific Time Zone
-The 2026 FIFA World Cup has completely tak</t>
+          <t>The awesome thing about a World Cup is that – unlike the Premier League where almost every elite-grade head coach comes from the same scenic Spanish t</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Today's World Cup 2026 Kickoff Times: Complete Mountain Time (MT) Schedule</t>
+          <t>The French aristocrat and the all-American idiot: Henry v Lalas is the World Cup’s most compelling battle</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>goal_pw</t>
+          <t>guardian</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>2026-06-21T16:35:30</t>
+          <t>Sun, 21 Jun 2026 09</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>https://www.goal.com/en/news/world-cup-2026-mountain-time-schedule/blt2141270bc47c494f</t>
+          <t>https://www.theguardian.com/football/2026/jun/21/thierry-henry-alexi-lalas-fox-world-cup</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>An all-you-need-to-know guide on how to watch every World Cup game broadcast live in the Mountain Time Zone
-The 2026 FIFA World Cup has completely ta</t>
+          <t xml:space="preserve">Fox’s broadcast at the tournament has become a story of two contrasting styles. And there is one clear winner  W e all know someone like Alexi Lalas. </t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Today's World Cup 2026 Kickoff Times: Complete Eastern Time (ET) Schedule</t>
+          <t>The 2026 World Cup team of the tournament so far (without the superstars)</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>goal_pw</t>
+          <t>guardian</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>2026-06-21T16:11:53</t>
+          <t>Sun, 21 Jun 2026 04</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>https://www.goal.com/en/news/world-cup-2026-eastern-time/blt57a4c6b10cc97d94</t>
+          <t>https://www.theguardian.com/football/2026/jun/21/the-2026-world-cup-team-of-the-tournament-so-far-without-the-superstars</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>An all-you-need-to-know guide on how to watch every World Cup game broadcast live in the Eastern Time Zone
-The 2026 FIFA World Cup has completely tak</t>
+          <t>We pick an XI of players who have impressed during the initial rounds of games in Canada, the US and Mexico  A star was born, at 40, when a player who</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Belgium vs Iran Prediction: World Cup 2026 Match Preview</t>
+          <t>Spain v Saudi Arabia: World Cup 2026 – live</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>theanalyst_api</t>
+          <t>guardian</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>2026-06-21T03:52:12</t>
+          <t>Sun Jun 21 2026 15:</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>https://theanalyst.com/articles/belgium-vs-iran-prediction-world-cup-2026-match-preview/</t>
+          <t>https://www.theguardian.com/football/live/2026/jun/21/spain-v-saudi-arabia-world-cup-2026-live</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>After a balanced start left both of these sides with just one point each from their opening FIFA World Cup fixtures, we look ahead to Sunday’s clash w</t>
+          <t>⚽️ Kick-off: 12pm local time/5pm BST/2am (Mon) AEST ⚽️ Player guide | Bracketology | Golden Boot | Email John  Alex Reid has penned today’s weekend sp</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Fastest World Cup to 100 goals in 68 years - are balls and breaks behind it?</t>
+          <t>Saibari strikes after 70 seconds as Morocco puncture Scotland’s World Cup party</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>bbc_sport</t>
+          <t>guardian</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>2026-06-20T23:46:26</t>
+          <t>Sat, 20 Jun 2026 00</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>https://www.bbc.com/sport/football/articles/cvglnkw1l93o?at_medium=RSS&amp;at_campaign=rss</t>
+          <t>https://www.theguardian.com/football/2026/jun/20/scotland-morocco-world-cup-match-report</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Messi, Mbappe and Vinicius Jr - the best World Cup goals from round one  The 2026 World Cup has become the fastest edition of the tournament to hit 10</t>
+          <t xml:space="preserve">Scotland would have taken this outcome after 70 seconds. Ismael Saibiri had fired this highly rated Morocco team ahead. Men in kilts gulped under the </t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>扎卡：替补证明了瑞士的阵容深度；罚点前我跟曼赞比说你还年轻</t>
+          <t>ITV wins World Cup ratings battle with BBC in tournament’s first week</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>dongqiudi_team</t>
+          <t>guardian</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>2026-06-20 04:57</t>
+          <t>Fri, 19 Jun 2026 10</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>https://www.dongqiudi.com/articles/5950591.html</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr"/>
+          <t>https://www.theguardian.com/football/2026/jun/19/itv-wins-world-cup-ratings-battle-bbc-first-week-england-croatia</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>England v Croatia attracted year’s highest UK TV figures  BBC opted for more first-pick games in knockout stages  ITV is winning the UK television rat</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>创造历史，加拿大是首支世界杯单场进6球的中北美球队</t>
+          <t>Name the seven Scotland survivors from Clarke's first squad</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>dongqiudi_team</t>
+          <t>bbc_sport</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>2026-06-20 04:29</t>
+          <t>2026-06-22T07:46:18</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>https://www.dongqiudi.com/articles/5950533.html</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr"/>
+          <t>https://www.bbc.com/sport/football/articles/c05yze49v71o?at_medium=RSS&amp;at_campaign=rss</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Seven years have passed since Steve Clarke named his first Scotland squad for Euro 2020 qualifiers against Cyprus and Belgium.  Seven players from tha</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Was Canada’s Win Over Qatar the Most One-Sided Game in World Cup History?</t>
+          <t>Scotland's 2026 World Cup squad: All 26 players picked by Steve Clarke and why</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>theanalyst_api</t>
+          <t>espn_pw</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>2026-06-19T15:12:21</t>
+          <t>2026-06-22T06:34:52</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>https://theanalyst.com/articles/canada-win-over-qatar-one-sided-world-cup-2026/</t>
+          <t>https://www.espn.com/soccer/story/_/id/48769157/meet-scotland-2026-world-cup-squad-all-26-players-picked-steve-clarke-why</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>It was wave after wave after wave, only Qatar’s second match at the 2026 FIFA World Cup was anything but a day at the beach.
-World Cup co-hosts Canad</t>
+          <t>Scotland manager Steve Clarke has named the 26 players he believes can make an impression at the 2026 World Cup in the United States, Canada and Mexic</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>World Cup 2026: Routes to the final</t>
+          <t>4-0突尼斯，日本终结连续5届世界杯小组赛第二轮不胜魔咒</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>fifa</t>
+          <t>dongqiudi</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>2026-06-19T12:00:00</t>
+          <t>2026-06-22 07:41</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>https://www.fifa.com/en/articles/group-stage-permutations-qualify</t>
+          <t>https://www.dongqiudi.com/article/5956343</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Find out what every team needs to qualify for the Round of 32 as group winners or runners-up, with information on Groups A-L, plus the tournament brac</t>
+          <t>世界杯小组赛第二轮，日本对阵突尼斯，最终日本国家队4-0大胜突尼斯。
+据统计，日本本轮大胜后终结了连续5届世界杯小组赛第二轮不胜魔咒，自2006年世界杯以来，日本队在世界杯小组赛第二轮未尝胜绩，本届世界杯终于打破魔咒。
+日本世界杯小组赛第二轮战绩
+1998 法国世界杯
+次轮：日本 0-1 克罗地亚（</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Canada 6-0 Qatar Stats: Hat-Trick Hero David Inspires Co-Hosts’ Historic First World Cup Win</t>
+          <t>Does it matter if Scotland lose and still make history?</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>theanalyst_api</t>
+          <t>bbc_sport</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>2026-06-19T00:20:51</t>
+          <t>2026-06-21T21:39:43</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>https://theanalyst.com/articles/canada-vs-qatar-stats-world-cup-2026-live/</t>
+          <t>https://www.bbc.com/sport/football/articles/ckg0exlle8yo?at_medium=RSS&amp;at_campaign=rss</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Co-hosts Canada put on a show in front of their fans in Vancouver, firing six goals past a nine-man Qatar to secure a 6-0 win; the biggest FIFA World </t>
+          <t>Steve Clarke and his squad are preparing for a potentially historic game  In a World Cup where the boffins with their big brainy heads and their super</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>盖村国家队战报：哲科卡蒂奇首发，十人波黑不敌瑞士</t>
+          <t>Scotland World Cup injury concerns as Aaron Hickey, Scott McKenna, Lewis Ferguson miss training</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>dongqiudi_team</t>
+          <t>espn_pw</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>2026-06-19 15:05</t>
+          <t>2026-06-21T21:00:44</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>https://www.dongqiudi.com/articles/5948740.html</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr"/>
+          <t>https://www.espn.com/soccer/story/_/id/49135824/scotland-injury-concerns-aaron-hickey-scott-mckenna-lewis-ferguson-miss-training-world-cup</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Aaron Hickey, Scott McKenna and Lewis Ferguson missed group training ahead of Scotland's final World Cup Group C fixture against Brazil on Wednesday.</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>大卫完成帽子戏法，加拿大6球大胜首尝世界杯胜果</t>
+          <t>What have we learned from Scotland's World Cup so far?</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>dongqiudi_team</t>
+          <t>bbc_sport</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>2026-06-19 11:11</t>
+          <t>2026-06-21T13:14:21</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>https://www.dongqiudi.com/articles/5948312.html</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr"/>
+          <t>https://www.bbc.com/sport/football/articles/c79yq0yx10ro?at_medium=RSS&amp;at_campaign=rss</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Steve Clarke is bidding to become the first manager to steer Scotland beyond the group stage of a major tournament  After two World Cup outings, Scotl</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>世界杯B组前两轮积分榜：加拿大居首，下轮前二直接较量</t>
+          <t>官方：巴西裁判阿巴蒂将执法世界杯瑞士vs加拿大</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -884,12 +898,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>2026-06-19 10:27</t>
+          <t>2026-06-21 20:48</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>https://www.dongqiudi.com/articles/5948244.html</t>
+          <t>https://www.dongqiudi.com/articles/5955280.html</t>
         </is>
       </c>
       <c r="E18" t="inlineStr"/>
@@ -897,24 +911,786 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Miro Muheim Injury: Still training apart</t>
+          <t>荷兰5球大胜瑞典，世界杯连续不败场次超越贝利时代巴西</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>rotowire</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr"/>
+          <t>dongqiudi_team</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>2026-06-21 20:21</t>
+        </is>
+      </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>https://www.rotowire.com/soccer/headlines/miro-muheim-injury-still-training-apart-520472</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>Written by RotoWire Staff
-Muheim (calf) continues to train separately from the Switzerland squad, spending the start of training sessions doing stren</t>
+          <t>https://www.dongqiudi.com/articles/5955233.html</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>巴媒：内马尔恢复有球训练，力争对苏格兰完成世界杯首秀</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>dongqiudi_team</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>2026-06-21 07:27</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>https://www.dongqiudi.com/articles/5953848.html</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Neymar set for Scotland return as Raphinha faces World Cup setback</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>sofascore</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>2026-06-20T16:28:34</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>https://www.sofascore.com/news/neymar-set-for-scotland-return-as-raphinha-faces-world-cup-setback</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Carlo Ancelotti has confirmed he expects Neymar to be available for Brazil’s final Group C match against Scotland at the World Cup. However, Raphinha </t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>How does qualification for the World Cup knockout stage work?</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>bbc_sport</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>2026-06-20T16:24:00</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>https://www.bbc.com/sport/football/articles/cp8l6zj8441o?at_medium=RSS&amp;at_campaign=rss</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>England are aiming to win Group L - but their potential path to the final is tricky  As the planet's elite footballers put every effort into qualifyin</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Cunha riding wave of success after brilliant Brazil brace</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>fifa</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>2026-06-20T05:40:00</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>https://www.fifa.com/en/articles/matheus-cunha-brazil-reaction-haiti</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Four years after missing out on Qatar 2022, surfing fan Matheus Cunha scored his first FIFA World Cup goals as Brazil beat Haiti 3-0.
+After waiting f</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>The best photos from Matchday 9</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>fifa</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>2026-06-20T05:00:00</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>https://www.fifa.com/en/articles/best-photos-matchday-9</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Enjoy an array of the best photos from the most recent round of fixtures at the FIFA World Cup 2026.
+Two USA fans dressed as bald eagles pose ahead o</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Six players climbing the FIFA Power Rankings</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>fifa</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>2026-06-20T04:00:00</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>https://www.fifa.com/en/articles/six-players-climbing-fifa-power-rankings</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">From Jonathan David and Matheus Cunha to Lucas Paqueta and Chris Richards, see which players have risen swiftly up the FIFA Power Rankings.
+Jonathan </t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Vinicius Jr. hits the ground running with Brazil</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>fifa</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>2026-06-20T04:00:00</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>https://www.fifa.com/en/articles/vinicius-jr-brazil-great-start</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>The No. 7 has been involved in all of Brazil's goals so far in the World Cup and has surpassed stars like Romario and Ronaldinho in efficiency per gam</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>巴西队美加墨周期纪实39：世界杯小组赛3-0轻取海地</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>dongqiudi_team</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>2026-06-20 17:59</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>https://www.dongqiudi.com/articles/5951203.html</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>老熟人来了，瓜迪奥拉现身世界杯球场看台观战苏格兰vs摩洛哥</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>dongqiudi_team</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>2026-06-20 14:52</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>https://www.dongqiudi.com/articles/5951666.html</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>巴西3-0海地登顶C组，卡塞米罗：世界杯无易战</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>dongqiudi_team</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>2026-06-20 12:56</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>https://www.dongqiudi.com/articles/5951477.html</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>世界杯积分新规，巴西3:0海地，海地成为第一支出...</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>dongqiudi_team</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>2026-06-20 10:46</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>https://www.dongqiudi.com/articles/5951242.html</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>8胜1平8次零封，巴西在世界杯面对中北美球队战绩碾压</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>dongqiudi_team</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>2026-06-20 07:12</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>https://www.dongqiudi.com/articles/5950880.html</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Brazil vs Haiti Prediction: World Cup 2026 Match Preview</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>theanalyst_api</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>2026-06-19T21:55:38</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>https://theanalyst.com/articles/brazil-vs-haiti-prediction-world-cup-2026-match-preview/</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Brazil are out to secure a first win of their World Cup 2026 campaign when they face off against Haiti in Philadelphia. Look ahead to the Group C cont</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Brazil vs Haiti preview: Group C stakes, key trends and a few numbers you’ll want to know</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>sofascore</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>2026-06-19T13:00:00</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>https://www.sofascore.com/news/brazil-vs-haiti-preview-group-c-stakes-key-trends-and-a-few-numbers-youll-want-to-know</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Brazil face Haiti in World Cup 2026 Group C. Form trends, key stats, decimal odds, team news and Sofascore Rating standouts to know before kickoff.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>World Cup 2026: Routes to the final</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>fifa</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>2026-06-19T12:00:00</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>https://www.fifa.com/en/articles/group-stage-permutations-qualify</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Find out what every team needs to qualify for the Round of 32 as group winners or runners-up, with information on Groups A-L, plus the tournament brac</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Scotland vs Morocco preview: World Cup Group C</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>sofascore</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>2026-06-19T12:00:00</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>https://www.sofascore.com/news/scotland-vs-morocco-preview-world-cup-group-c</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Scotland face Morocco at Gillette Stadium in World Cup 2026 Group C. Form, H2H, odds, lineups and the key Sofascore Rating standouts set the stage.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Scotland vs Morocco Prediction: World Cup 2026 Match Preview</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>theanalyst_api</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>2026-06-19T08:13:48</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>https://theanalyst.com/articles/scotland-vs-morocco-prediction-world-cup-2026-match-preview/</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>After a pair of exciting curtain-raisers, the top two sides in Group C will now face off in Boston. Look ahead to Friday’s FIFA World Cup clash with o</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>How sweltering Scotland can handle World Cup heat</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>bbc_sport</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>2026-06-17T11:16:20</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>https://www.bbc.com/sport/football/articles/cx26geg0elgo?at_medium=RSS&amp;at_campaign=rss</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Scotland will face sweltering conditions in their final Group C match  Hydration breaks, ice jackets, cooling towels and isotonic drinks have been a f</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>联手梅西！罗马诺：卡塞米罗还收到欧洲沙特报价 他与迈阿密签3年</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>zhibo8</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>2026-06-22 15:35:00</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>https://m.zhibo8.com/news/web/zuqiu/2026-06-22/6a38e37c69ad1native.htm</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>帕奎塔：和维尼修斯一起踢球很快乐；我们都为内马尔回归高兴</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>dongqiudi_team</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>2026-06-22 03:33</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>https://www.dongqiudi.com/articles/5955960.html</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>ESPN：内马尔将入选对阵苏格兰比赛名单，但不会扮演重要角色</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>dongqiudi_team</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>2026-06-22 00:48</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>https://www.dongqiudi.com/articles/5955754.html</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>TA：巴西全民紧盯内马尔和恩德里克，真正的救星却是库尼亚</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>dongqiudi_team</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>2026-06-22 00:02</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>https://www.dongqiudi.com/articles/5955612.html</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>利物浦球员国家队战报：阿利松80场里程碑多次扑救+零封</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>dongqiudi_team</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>2026-06-20 11:15</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>https://www.dongqiudi.com/articles/5951315.html</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Maybe this World Cup will bring the best out of the US, not the worst</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>guardian</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Mon, 22 Jun 2026 04</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>https://www.theguardian.com/football/2026/jun/22/world-cup-2026-us-united-states-usa-co-host-nation</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>Tournament could hold up a useful hand mirror to the isolationism and divisiveness of Trump’s joint-host nation  O ne of the best parts of following f</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>World Cup 2026 fixtures and results: Every fixture and kick-off time for the biggest World Cup ever</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>squawka</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>6 days ago</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>https://www.squawka.com/en/news/world-cup/world-cup-2026-fixtures-results/</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The 2026 World Cup is now well underway. Find the latest World Cup results and upcoming fixtures here.
+Get the latest World Cup Group A betting odds </t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>What did we learn after the second round of Group C</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>sofascore</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>2026-06-21T15:21:15</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>https://www.sofascore.com/news/what-did-we-learn-after-the-second-round-of-group-c</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Aimar: Messi has made us expect the unexpected</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>fifa</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>2026-06-21T03:30:00</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>https://www.fifa.com/en/articles/pablo-aimar-messi</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>Lionel Scaloni’s assistant on the Argentina bench discusses his relationship with the captain and La Albiceleste’s recent success.
+At the age of 12 o</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Scotland 0-1 Morocco Stats: Early Saibari Stunner Settles Group C Clash</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>theanalyst</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>2026-06-20T01:12:39</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>https://theanalyst.com/articles/scotland-vs-morocco-stats-fifa-world-cup-2026-live</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>Follow the action live as Scotland look to make it two wins from two at the 2026 FIFA World Cup against African giants Morocco.</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>C组积分榜：巴西积4分领先摩洛哥2粒净胜球，海地提前出局</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>dongqiudi_team</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>2026-06-20 10:44</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>https://www.dongqiudi.com/articles/5951239.html</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Spain World Cup 2026: Fixtures, results, manager, squad depth and tactical analysis</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>squawka</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>15 hours ago</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>https://www.squawka.com/en/news/world-cup/spain-world-cup-2026-fixtures-results-squad-analysis/</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>Spain ’s 2026 World Cup campaign took a sharp turn in North America as they followed up a frustrating opening draw with Cape Verde by producing a comm</t>
         </is>
       </c>
     </row>
@@ -929,7 +1705,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E30"/>
+  <dimension ref="A1:E37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="60" customWidth="1" min="1" max="1"/>
@@ -1685,6 +2461,193 @@
         </is>
       </c>
       <c r="E30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Maybe this World Cup will bring the best out of the US, not the worst</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>guardian</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Mon, 22 Jun 2026 04</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>https://www.theguardian.com/football/2026/jun/22/world-cup-2026-us-united-states-usa-co-host-nation</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Tournament could hold up a useful hand mirror to the isolationism and divisiveness of Trump’s joint-host nation  O ne of the best parts of following f</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>World Cup 2026 fixtures and results: Every fixture and kick-off time for the biggest World Cup ever</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>squawka</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>6 days ago</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>https://www.squawka.com/en/news/world-cup/world-cup-2026-fixtures-results/</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The 2026 World Cup is now well underway. Find the latest World Cup results and upcoming fixtures here.
+Get the latest World Cup Group A betting odds </t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>What did we learn after the second round of Group C</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>sofascore</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>2026-06-21T15:21:15</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>https://www.sofascore.com/news/what-did-we-learn-after-the-second-round-of-group-c</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Aimar: Messi has made us expect the unexpected</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>fifa</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>2026-06-21T03:30:00</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>https://www.fifa.com/en/articles/pablo-aimar-messi</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Lionel Scaloni’s assistant on the Argentina bench discusses his relationship with the captain and La Albiceleste’s recent success.
+At the age of 12 o</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>How does qualification for the World Cup knockout stage work?</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>bbc_sport</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>2026-06-20T16:24:00</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>https://www.bbc.com/sport/football/articles/cp8l6zj8441o?at_medium=RSS&amp;at_campaign=rss</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>England are aiming to win Group L - but their potential path to the final is tricky  As the planet's elite footballers put every effort into qualifyin</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Scotland 0-1 Morocco Stats: Early Saibari Stunner Settles Group C Clash</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>theanalyst</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>2026-06-20T01:12:39</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>https://theanalyst.com/articles/scotland-vs-morocco-stats-fifa-world-cup-2026-live</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Follow the action live as Scotland look to make it two wins from two at the 2026 FIFA World Cup against African giants Morocco.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Spain World Cup 2026: Fixtures, results, manager, squad depth and tactical analysis</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>squawka</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>15 hours ago</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>https://www.squawka.com/en/news/world-cup/spain-world-cup-2026-fixtures-results-squad-analysis/</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Spain ’s 2026 World Cup campaign took a sharp turn in North America as they followed up a frustrating opening draw with Cape Verde by producing a comm</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1697,7 +2660,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E41"/>
+  <dimension ref="A1:E29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="60" customWidth="1" min="1" max="1"/>
@@ -1735,435 +2698,423 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Neymar completes first World Cup training session before Brazil vs. Scotland</t>
+          <t>官方：巴西裁判阿巴蒂将执法世界杯瑞士vs加拿大</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>espn_pw</t>
+          <t>dongqiudi_team</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2026-06-22T08:40:32</t>
+          <t>2026-06-21 20:48</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>https://www.espn.com/soccer/story/_/id/49142107/neymar-completes-first-world-cup-training-session-brazil-vs-scotland</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>Neymar completed his first full training session with Brazil on Sunday.</t>
-        </is>
-      </c>
+          <t>https://www.dongqiudi.com/articles/5955280.html</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Lucas Paqueta: Brazil have 'great respect' for Scotland</t>
+          <t>World Cup 2026 news and live updates - USA, Canada and Mexico latest including Trump, tickets and fans</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>espn_pw</t>
+          <t>skysports</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2026-06-21T23:39:02</t>
+          <t>Sun, 21 Jun 2026 15</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>https://www.espn.com/soccer/story/_/id/49138795/lucas-paqueta-brazil-scotland-fifa-world-cup-2026</t>
+          <t>https://www.skysports.com/football/live-blog/12040/13509050/world-cup-2026-news-and-live-updates-usa-canada-and-mexico-latest-including-trump-tickets-and-fans</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Brazil playmaker Lucas Paquetá says he has "great respect" for Scotland ahead of the decisive clash between the teams in Miami on Wednesday.</t>
+          <t>Update World Cup 2026 news and live updates - USA, Canada and Mexico latest including Trump, tickets and fans Sunday 21 June 2026 15:14, UK Sorry, thi</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>官方：墨西哥裁判拉莫斯将执法世界杯苏格兰vs巴西</t>
+          <t>The 2026 World Cup team of the tournament so far (without the superstars)</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>dongqiudi_team</t>
+          <t>guardian</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2026-06-21 20:39</t>
+          <t>Sun, 21 Jun 2026 04</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>https://www.dongqiudi.com/articles/5955264.html</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr"/>
+          <t>https://www.theguardian.com/football/2026/jun/21/the-2026-world-cup-team-of-the-tournament-so-far-without-the-superstars</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>We pick an XI of players who have impressed during the initial rounds of games in Canada, the US and Mexico  A star was born, at 40, when a player who</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>苏格兰主帅：对摩洛哥我们踢得有点慢热；末轮要死磕巴西</t>
+          <t>How to watch Germany vs Ivory Coast for FREE: Live stream details &amp; TV channels for World Cup 2026 as Kai Havertz tries to add to tally</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>dongqiudi_team</t>
+          <t>fourfourtwo</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2026-06-21 00:26</t>
+          <t>Sat, 20 Jun 2026 18</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>https://www.dongqiudi.com/articles/5953238.html</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr"/>
+          <t>https://www.fourfourtwo.com/competition/watch-germany-vs-ivory-coast-free-world-cup-2026</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Germany and the Ivory Coast may have won their respective opening games at the World Cup 2026 , but the contrasting manner in which they each delivere</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Guns for hire and gegenpress eggheads bring World Cup subplots aplenty</t>
+          <t>Today's World Cup 2026 Kickoff Times: Complete Pacific Time (PT) Schedule</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>guardian</t>
+          <t>goal_pw</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Sun, 21 Jun 2026 13</t>
+          <t>2026-06-21T17:04:43</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>https://www.theguardian.com/football/2026/jun/21/football-daily-geopolitics-world-cup-maverick-managerial-matchups</t>
+          <t>https://www.goal.com/en/news/world-cup-2026-pacific-time-schedule/blt708391eb6f8f1517</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>The awesome thing about a World Cup is that – unlike the Premier League where almost every elite-grade head coach comes from the same scenic Spanish t</t>
+          <t>An all-you-need-to-know guide on how to watch every World Cup game broadcast live in the Pacific Time Zone
+The 2026 FIFA World Cup has completely tak</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>The French aristocrat and the all-American idiot: Henry v Lalas is the World Cup’s most compelling battle</t>
+          <t>Today's World Cup 2026 Kickoff Times: Complete Mountain Time (MT) Schedule</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>guardian</t>
+          <t>goal_pw</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Sun, 21 Jun 2026 09</t>
+          <t>2026-06-21T16:35:30</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>https://www.theguardian.com/football/2026/jun/21/thierry-henry-alexi-lalas-fox-world-cup</t>
+          <t>https://www.goal.com/en/news/world-cup-2026-mountain-time-schedule/blt2141270bc47c494f</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fox’s broadcast at the tournament has become a story of two contrasting styles. And there is one clear winner  W e all know someone like Alexi Lalas. </t>
+          <t>An all-you-need-to-know guide on how to watch every World Cup game broadcast live in the Mountain Time Zone
+The 2026 FIFA World Cup has completely ta</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>The 2026 World Cup team of the tournament so far (without the superstars)</t>
+          <t>Today's World Cup 2026 Kickoff Times: Complete Eastern Time (ET) Schedule</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>guardian</t>
+          <t>goal_pw</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Sun, 21 Jun 2026 04</t>
+          <t>2026-06-21T16:11:53</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>https://www.theguardian.com/football/2026/jun/21/the-2026-world-cup-team-of-the-tournament-so-far-without-the-superstars</t>
+          <t>https://www.goal.com/en/news/world-cup-2026-eastern-time/blt57a4c6b10cc97d94</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>We pick an XI of players who have impressed during the initial rounds of games in Canada, the US and Mexico  A star was born, at 40, when a player who</t>
+          <t>An all-you-need-to-know guide on how to watch every World Cup game broadcast live in the Eastern Time Zone
+The 2026 FIFA World Cup has completely tak</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Spain v Saudi Arabia: World Cup 2026 – live</t>
+          <t>Belgium vs Iran Prediction: World Cup 2026 Match Preview</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>guardian</t>
+          <t>theanalyst_api</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Sun Jun 21 2026 15:</t>
+          <t>2026-06-21T03:52:12</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>https://www.theguardian.com/football/live/2026/jun/21/spain-v-saudi-arabia-world-cup-2026-live</t>
+          <t>https://theanalyst.com/articles/belgium-vs-iran-prediction-world-cup-2026-match-preview/</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>⚽️ Kick-off: 12pm local time/5pm BST/2am (Mon) AEST ⚽️ Player guide | Bracketology | Golden Boot | Email John  Alex Reid has penned today’s weekend sp</t>
+          <t>After a balanced start left both of these sides with just one point each from their opening FIFA World Cup fixtures, we look ahead to Sunday’s clash w</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Saibari strikes after 70 seconds as Morocco puncture Scotland’s World Cup party</t>
+          <t>Fastest World Cup to 100 goals in 68 years - are balls and breaks behind it?</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>guardian</t>
+          <t>bbc_sport</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Sat, 20 Jun 2026 00</t>
+          <t>2026-06-20T23:46:26</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>https://www.theguardian.com/football/2026/jun/20/scotland-morocco-world-cup-match-report</t>
+          <t>https://www.bbc.com/sport/football/articles/cvglnkw1l93o?at_medium=RSS&amp;at_campaign=rss</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Scotland would have taken this outcome after 70 seconds. Ismael Saibiri had fired this highly rated Morocco team ahead. Men in kilts gulped under the </t>
+          <t>Messi, Mbappe and Vinicius Jr - the best World Cup goals from round one  The 2026 World Cup has become the fastest edition of the tournament to hit 10</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>ITV wins World Cup ratings battle with BBC in tournament’s first week</t>
+          <t>扎卡：替补证明了瑞士的阵容深度；罚点前我跟曼赞比说你还年轻</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>guardian</t>
+          <t>dongqiudi_team</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Fri, 19 Jun 2026 10</t>
+          <t>2026-06-20 04:57</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>https://www.theguardian.com/football/2026/jun/19/itv-wins-world-cup-ratings-battle-bbc-first-week-england-croatia</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>England v Croatia attracted year’s highest UK TV figures  BBC opted for more first-pick games in knockout stages  ITV is winning the UK television rat</t>
-        </is>
-      </c>
+          <t>https://www.dongqiudi.com/articles/5950591.html</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Name the seven Scotland survivors from Clarke's first squad</t>
+          <t>创造历史，加拿大是首支世界杯单场进6球的中北美球队</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>bbc_sport</t>
+          <t>dongqiudi_team</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>2026-06-22T07:46:18</t>
+          <t>2026-06-20 04:29</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>https://www.bbc.com/sport/football/articles/c05yze49v71o?at_medium=RSS&amp;at_campaign=rss</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>Seven years have passed since Steve Clarke named his first Scotland squad for Euro 2020 qualifiers against Cyprus and Belgium.  Seven players from tha</t>
-        </is>
-      </c>
+          <t>https://www.dongqiudi.com/articles/5950533.html</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Scotland's 2026 World Cup squad: All 26 players picked by Steve Clarke and why</t>
+          <t>Was Canada’s Win Over Qatar the Most One-Sided Game in World Cup History?</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>espn_pw</t>
+          <t>theanalyst_api</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>2026-06-22T06:34:52</t>
+          <t>2026-06-19T15:12:21</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>https://www.espn.com/soccer/story/_/id/48769157/meet-scotland-2026-world-cup-squad-all-26-players-picked-steve-clarke-why</t>
+          <t>https://theanalyst.com/articles/canada-win-over-qatar-one-sided-world-cup-2026/</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Scotland manager Steve Clarke has named the 26 players he believes can make an impression at the 2026 World Cup in the United States, Canada and Mexic</t>
+          <t>It was wave after wave after wave, only Qatar’s second match at the 2026 FIFA World Cup was anything but a day at the beach.
+World Cup co-hosts Canad</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>4-0突尼斯，日本终结连续5届世界杯小组赛第二轮不胜魔咒</t>
+          <t>World Cup 2026: Routes to the final</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>dongqiudi</t>
+          <t>fifa</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>2026-06-22 07:41</t>
+          <t>2026-06-19T12:00:00</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>https://www.dongqiudi.com/article/5956343</t>
+          <t>https://www.fifa.com/en/articles/group-stage-permutations-qualify</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>世界杯小组赛第二轮，日本对阵突尼斯，最终日本国家队4-0大胜突尼斯。
-据统计，日本本轮大胜后终结了连续5届世界杯小组赛第二轮不胜魔咒，自2006年世界杯以来，日本队在世界杯小组赛第二轮未尝胜绩，本届世界杯终于打破魔咒。
-日本世界杯小组赛第二轮战绩
-1998 法国世界杯
-次轮：日本 0-1 克罗地亚（</t>
+          <t>Find out what every team needs to qualify for the Round of 32 as group winners or runners-up, with information on Groups A-L, plus the tournament brac</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Does it matter if Scotland lose and still make history?</t>
+          <t>Canada 6-0 Qatar Stats: Hat-Trick Hero David Inspires Co-Hosts’ Historic First World Cup Win</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>bbc_sport</t>
+          <t>theanalyst_api</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>2026-06-21T21:39:43</t>
+          <t>2026-06-19T00:20:51</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>https://www.bbc.com/sport/football/articles/ckg0exlle8yo?at_medium=RSS&amp;at_campaign=rss</t>
+          <t>https://theanalyst.com/articles/canada-vs-qatar-stats-world-cup-2026-live/</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Steve Clarke and his squad are preparing for a potentially historic game  In a World Cup where the boffins with their big brainy heads and their super</t>
+          <t xml:space="preserve">Co-hosts Canada put on a show in front of their fans in Vancouver, firing six goals past a nine-man Qatar to secure a 6-0 win; the biggest FIFA World </t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Scotland World Cup injury concerns as Aaron Hickey, Scott McKenna, Lewis Ferguson miss training</t>
+          <t>盖村国家队战报：哲科卡蒂奇首发，十人波黑不敌瑞士</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>espn_pw</t>
+          <t>dongqiudi_team</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>2026-06-21T21:00:44</t>
+          <t>2026-06-19 15:05</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>https://www.espn.com/soccer/story/_/id/49135824/scotland-injury-concerns-aaron-hickey-scott-mckenna-lewis-ferguson-miss-training-world-cup</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>Aaron Hickey, Scott McKenna and Lewis Ferguson missed group training ahead of Scotland's final World Cup Group C fixture against Brazil on Wednesday.</t>
-        </is>
-      </c>
+          <t>https://www.dongqiudi.com/articles/5948740.html</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>What have we learned from Scotland's World Cup so far?</t>
+          <t>大卫完成帽子戏法，加拿大6球大胜首尝世界杯胜果</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>bbc_sport</t>
+          <t>dongqiudi_team</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>2026-06-21T13:14:21</t>
+          <t>2026-06-19 11:11</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>https://www.bbc.com/sport/football/articles/c79yq0yx10ro?at_medium=RSS&amp;at_campaign=rss</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>Steve Clarke is bidding to become the first manager to steer Scotland beyond the group stage of a major tournament  After two World Cup outings, Scotl</t>
-        </is>
-      </c>
+          <t>https://www.dongqiudi.com/articles/5948312.html</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>官方：巴西裁判阿巴蒂将执法世界杯瑞士vs加拿大</t>
+          <t>世界杯B组前两轮积分榜：加拿大居首，下轮前二直接较量</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2173,12 +3124,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>2026-06-21 20:48</t>
+          <t>2026-06-19 10:27</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>https://www.dongqiudi.com/articles/5955280.html</t>
+          <t>https://www.dongqiudi.com/articles/5948244.html</t>
         </is>
       </c>
       <c r="E18" t="inlineStr"/>
@@ -2186,191 +3137,194 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>荷兰5球大胜瑞典，世界杯连续不败场次超越贝利时代巴西</t>
+          <t>Belgium vs Iran Bet Builder Tip: Consider Belgium to bounce back with 25/1 multi</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>dongqiudi_team</t>
+          <t>squawka</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>2026-06-21 20:21</t>
+          <t>16 hours ago</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>https://www.dongqiudi.com/articles/5955233.html</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr"/>
+          <t>https://www.squawka.com/en/news/world-cup/belgium-vs-iran-bet-builder-21-06-26-world-cup/</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Belgium will be looking to respond after a frustrating opening draw against Egypt when they face Iran at the 2026 World Cup on Sunday night. Read on f</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>巴媒：内马尔恢复有球训练，力争对苏格兰完成世界杯首秀</t>
+          <t>Miro Muheim Injury: Still training apart</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>dongqiudi_team</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>2026-06-21 07:27</t>
-        </is>
-      </c>
+          <t>rotowire</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr"/>
       <c r="D20" t="inlineStr">
         <is>
-          <t>https://www.dongqiudi.com/articles/5953848.html</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr"/>
+          <t>https://www.rotowire.com/soccer/headlines/miro-muheim-injury-still-training-apart-520472</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Written by RotoWire Staff
+Muheim (calf) continues to train separately from the Switzerland squad, spending the start of training sessions doing stren</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Neymar set for Scotland return as Raphinha faces World Cup setback</t>
+          <t>Shocking Sunderland stat re-emerges, following Brian Brobbey masterclass</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>sofascore</t>
+          <t>fourfourtwo</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>2026-06-20T16:28:34</t>
+          <t>Sat, 20 Jun 2026 20</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>https://www.sofascore.com/news/neymar-set-for-scotland-return-as-raphinha-faces-world-cup-setback</t>
+          <t>https://www.fourfourtwo.com/competition/which-clubs-do-sunderland-have-more-players-than-at-the-2026-world-cup</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t xml:space="preserve">Carlo Ancelotti has confirmed he expects Neymar to be available for Brazil’s final Group C match against Scotland at the World Cup. However, Raphinha </t>
+          <t>In 2017/18, when Manchester City won the Premier League with 100 points, Sunderland were acclimating to Championship life.  The season prior, when Che</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>How does qualification for the World Cup knockout stage work?</t>
+          <t>Women’s T20 World Cup: West Indies defeat Sri Lanka by five wickets to stay unbeaten ahead of crunch England match</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>bbc_sport</t>
+          <t>skysports</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>2026-06-20T16:24:00</t>
+          <t>Sat, 20 Jun 2026 14</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>https://www.bbc.com/sport/football/articles/cp8l6zj8441o?at_medium=RSS&amp;at_campaign=rss</t>
+          <t>https://www.skysports.com/cricket/news/12040/13556291/womens-t20-world-cup-west-indies-defeat-sri-lanka-by-five-wickets-to-stay-unbeaten-ahead-of-crunch-england-match</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>England are aiming to win Group L - but their potential path to the final is tricky  As the planet's elite footballers put every effort into qualifyin</t>
+          <t>Captain Hayley Matthews and Stafanie Taylor lead the way for West Indies, who join England on six points atop Group B after five-wicket win in low-sco</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Cunha riding wave of success after brilliant Brazil brace</t>
+          <t>How far can the USA go at the 2026 World Cup? Hugely favourable route to semi-finals revealed</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>fifa</t>
+          <t>fourfourtwo</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>2026-06-20T05:40:00</t>
+          <t>Mon, 22 Jun 2026 08</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>https://www.fifa.com/en/articles/matheus-cunha-brazil-reaction-haiti</t>
+          <t>https://www.fourfourtwo.com/team/how-far-can-the-usa-go-at-the-2026-world-cup-hugely-favourable-route-to-semi-finals-revealed</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Four years after missing out on Qatar 2022, surfing fan Matheus Cunha scored his first FIFA World Cup goals as Brazil beat Haiti 3-0.
-After waiting f</t>
+          <t xml:space="preserve">As the group stage of the 2026 FIFA World Cup nears its conclusion, the United States Men’s National Team (USMNT) have positioned themselves strongly </t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>The best photos from Matchday 9</t>
+          <t>New Zealand World Cup 2026: Fixtures, manager, squad depth and tactical analysis</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>fifa</t>
+          <t>squawka</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>2026-06-20T05:00:00</t>
+          <t>7 hours ago</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>https://www.fifa.com/en/articles/best-photos-matchday-9</t>
+          <t>https://www.squawka.com/en/news/world-cup/new-zealand-world-cup-2026-fixtures-squad-analysis/</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Enjoy an array of the best photos from the most recent round of fixtures at the FIFA World Cup 2026.
-Two USA fans dressed as bald eagles pose ahead o</t>
+          <t>This summer marks New Zealand’s third appearance at a World Cup . They went unbeaten in their most recent appearance in 2010, but three draws wasn’t e</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Six players climbing the FIFA Power Rankings</t>
+          <t>World Cup 2026 fixtures and results: Every fixture and kick-off time for the biggest World Cup ever</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>fifa</t>
+          <t>squawka</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>2026-06-20T04:00:00</t>
+          <t>6 days ago</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>https://www.fifa.com/en/articles/six-players-climbing-fifa-power-rankings</t>
+          <t>https://www.squawka.com/en/news/world-cup/world-cup-2026-fixtures-results/</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t xml:space="preserve">From Jonathan David and Matheus Cunha to Lucas Paqueta and Chris Richards, see which players have risen swiftly up the FIFA Power Rankings.
-Jonathan </t>
+          <t xml:space="preserve">The 2026 World Cup is now well underway. Find the latest World Cup results and upcoming fixtures here.
+Get the latest World Cup Group A betting odds </t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Vinicius Jr. hits the ground running with Brazil</t>
+          <t>Spain send statement with Saudi success</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2380,388 +3334,101 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>2026-06-20T04:00:00</t>
+          <t>2026-06-21T18:00:00</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>https://www.fifa.com/en/articles/vinicius-jr-brazil-great-start</t>
+          <t>https://www.fifa.com/en/articles/spain-saudi-arabia-highlights-match-report</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>The No. 7 has been involved in all of Brazil's goals so far in the World Cup and has surpassed stars like Romario and Ronaldinho in efficiency per gam</t>
+          <t>This is a modal window.
+Oyarzabal and Yamal on target in dominant display as Luis de la Fuente's side showed their class with a comprehensive Group H</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>巴西队美加墨周期纪实39：世界杯小组赛3-0轻取海地</t>
+          <t>Brazil vs Haiti Prediction: World Cup 2026 Match Preview</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>dongqiudi_team</t>
+          <t>theanalyst_api</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>2026-06-20 17:59</t>
+          <t>2026-06-19T21:55:38</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>https://www.dongqiudi.com/articles/5951203.html</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr"/>
+          <t>https://theanalyst.com/articles/brazil-vs-haiti-prediction-world-cup-2026-match-preview/</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Brazil are out to secure a first win of their World Cup 2026 campaign when they face off against Haiti in Philadelphia. Look ahead to the Group C cont</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>老熟人来了，瓜迪奥拉现身世界杯球场看台观战苏格兰vs摩洛哥</t>
+          <t>Group B: What did we learn in the second round?</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>dongqiudi_team</t>
+          <t>sofascore</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>2026-06-20 14:52</t>
+          <t>2026-06-19T13:54:58</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>https://www.dongqiudi.com/articles/5951666.html</t>
-        </is>
-      </c>
-      <c r="E28" t="inlineStr"/>
+          <t>https://www.sofascore.com/news/group-b-what-did-we-learn-in-the-second-round</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Canada and Switzerland seized control of Group B with statement wins, while Bosnia and Qatar now face a decisive fight for survival.</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>巴西3-0海地登顶C组，卡塞米罗：世界杯无易战</t>
+          <t>Uruguay vs Cape Verde Bet Builder: Uruguay to dominate in our 13/1 tip for tonight</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>dongqiudi_team</t>
+          <t>squawka</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>2026-06-20 12:56</t>
+          <t>13 hours ago</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>https://www.dongqiudi.com/articles/5951477.html</t>
-        </is>
-      </c>
-      <c r="E29" t="inlineStr"/>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>世界杯积分新规，巴西3:0海地，海地成为第一支出...</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>dongqiudi_team</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>2026-06-20 10:46</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>https://www.dongqiudi.com/articles/5951242.html</t>
-        </is>
-      </c>
-      <c r="E30" t="inlineStr"/>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>8胜1平8次零封，巴西在世界杯面对中北美球队战绩碾压</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>dongqiudi_team</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>2026-06-20 07:12</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>https://www.dongqiudi.com/articles/5950880.html</t>
-        </is>
-      </c>
-      <c r="E31" t="inlineStr"/>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>Brazil vs Haiti Prediction: World Cup 2026 Match Preview</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>theanalyst_api</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>2026-06-19T21:55:38</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>https://theanalyst.com/articles/brazil-vs-haiti-prediction-world-cup-2026-match-preview/</t>
-        </is>
-      </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>Brazil are out to secure a first win of their World Cup 2026 campaign when they face off against Haiti in Philadelphia. Look ahead to the Group C cont</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>Brazil vs Haiti preview: Group C stakes, key trends and a few numbers you’ll want to know</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>sofascore</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>2026-06-19T13:00:00</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>https://www.sofascore.com/news/brazil-vs-haiti-preview-group-c-stakes-key-trends-and-a-few-numbers-youll-want-to-know</t>
-        </is>
-      </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>Brazil face Haiti in World Cup 2026 Group C. Form trends, key stats, decimal odds, team news and Sofascore Rating standouts to know before kickoff.</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>World Cup 2026: Routes to the final</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>fifa</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>2026-06-19T12:00:00</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>https://www.fifa.com/en/articles/group-stage-permutations-qualify</t>
-        </is>
-      </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>Find out what every team needs to qualify for the Round of 32 as group winners or runners-up, with information on Groups A-L, plus the tournament brac</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>Scotland vs Morocco preview: World Cup Group C</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>sofascore</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>2026-06-19T12:00:00</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>https://www.sofascore.com/news/scotland-vs-morocco-preview-world-cup-group-c</t>
-        </is>
-      </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>Scotland face Morocco at Gillette Stadium in World Cup 2026 Group C. Form, H2H, odds, lineups and the key Sofascore Rating standouts set the stage.</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>Scotland vs Morocco Prediction: World Cup 2026 Match Preview</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>theanalyst_api</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>2026-06-19T08:13:48</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>https://theanalyst.com/articles/scotland-vs-morocco-prediction-world-cup-2026-match-preview/</t>
-        </is>
-      </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>After a pair of exciting curtain-raisers, the top two sides in Group C will now face off in Boston. Look ahead to Friday’s FIFA World Cup clash with o</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>How sweltering Scotland can handle World Cup heat</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>bbc_sport</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>2026-06-17T11:16:20</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>https://www.bbc.com/sport/football/articles/cx26geg0elgo?at_medium=RSS&amp;at_campaign=rss</t>
-        </is>
-      </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>Scotland will face sweltering conditions in their final Group C match  Hydration breaks, ice jackets, cooling towels and isotonic drinks have been a f</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>帕奎塔：和维尼修斯一起踢球很快乐；我们都为内马尔回归高兴</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>dongqiudi_team</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>2026-06-22 03:33</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>https://www.dongqiudi.com/articles/5955960.html</t>
-        </is>
-      </c>
-      <c r="E38" t="inlineStr"/>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>ESPN：内马尔将入选对阵苏格兰比赛名单，但不会扮演重要角色</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>dongqiudi_team</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>2026-06-22 00:48</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>https://www.dongqiudi.com/articles/5955754.html</t>
-        </is>
-      </c>
-      <c r="E39" t="inlineStr"/>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>TA：巴西全民紧盯内马尔和恩德里克，真正的救星却是库尼亚</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>dongqiudi_team</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>2026-06-22 00:02</t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>https://www.dongqiudi.com/articles/5955612.html</t>
-        </is>
-      </c>
-      <c r="E40" t="inlineStr"/>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>利物浦球员国家队战报：阿利松80场里程碑多次扑救+零封</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>dongqiudi_team</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>2026-06-20 11:15</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>https://www.dongqiudi.com/articles/5951315.html</t>
-        </is>
-      </c>
-      <c r="E41" t="inlineStr"/>
+          <t>https://www.squawka.com/en/news/world-cup/uruguay-vs-cape-verde-bet-builder-21-06-2026/</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Uruguay will look to bring Cape Verde ‘s impressive unbeaten start to the 2026 World Cup to an end when the two nations meet in Group H at Hard Rock S</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2774,7 +3441,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E16"/>
+  <dimension ref="A1:E22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="60" customWidth="1" min="1" max="1"/>
@@ -2812,7 +3479,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>官方：阿根廷裁判法尔孔将执法世界杯捷克vs墨西哥</t>
+          <t>官方：委内瑞拉裁判巴伦苏埃拉将执法世界杯波黑vs卡塔尔</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -2822,12 +3489,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2026-06-21 20:50</t>
+          <t>2026-06-21 20:45</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>https://www.dongqiudi.com/articles/5955283.html</t>
+          <t>https://www.dongqiudi.com/articles/5955276.html</t>
         </is>
       </c>
       <c r="E2" t="inlineStr"/>
@@ -2835,83 +3502,682 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>World Cup 2026 news and live updates - USA, Canada and Mexico latest including Trump, tickets and fans</t>
+          <t>The 2026 World Cup team of the tournament so far (without the superstars)</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>skysports</t>
+          <t>guardian</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Sun, 21 Jun 2026 15</t>
+          <t>Sun, 21 Jun 2026 04</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>https://www.skysports.com/football/live-blog/12040/13509050/world-cup-2026-news-and-live-updates-usa-canada-and-mexico-latest-including-trump-tickets-and-fans</t>
+          <t>https://www.theguardian.com/football/2026/jun/21/the-2026-world-cup-team-of-the-tournament-so-far-without-the-superstars</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Update World Cup 2026 news and live updates - USA, Canada and Mexico latest including Trump, tickets and fans Sunday 21 June 2026 15:14, UK Sorry, thi</t>
+          <t>We pick an XI of players who have impressed during the initial rounds of games in Canada, the US and Mexico  A star was born, at 40, when a player who</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Giant Czech flag swallows World Cup staff member after national anthems</t>
+          <t>Today's World Cup 2026 Kickoff Times: Complete Pacific Time (PT) Schedule</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>fourfourtwo</t>
+          <t>goal_pw</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Sun, 21 Jun 2026 05</t>
+          <t>2026-06-21T17:04:43</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>https://www.fourfourtwo.com/competition/giant-czech-flag-swallows-world-cup-staff-member-after-national-anthems</t>
+          <t>https://www.goal.com/en/news/world-cup-2026-pacific-time-schedule/blt708391eb6f8f1517</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>We all loved playing parachute games at school, but the idea of being unexpectedly involved in one against your will is a terrifying prospect, as we'r</t>
+          <t>An all-you-need-to-know guide on how to watch every World Cup game broadcast live in the Pacific Time Zone
+The 2026 FIFA World Cup has completely tak</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>墨西哥前区长世界杯热舞，大方回应着装争议</t>
+          <t>Today's World Cup 2026 Kickoff Times: Complete Mountain Time (MT) Schedule</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>dongqiudi_team</t>
+          <t>goal_pw</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2026-06-22 11:19</t>
+          <t>2026-06-21T16:35:30</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>https://www.dongqiudi.com/articles/5956722.html</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr"/>
+          <t>https://www.goal.com/en/news/world-cup-2026-mountain-time-schedule/blt2141270bc47c494f</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>An all-you-need-to-know guide on how to watch every World Cup game broadcast live in the Mountain Time Zone
+The 2026 FIFA World Cup has completely ta</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>Today's World Cup 2026 Kickoff Times: Complete Eastern Time (ET) Schedule</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>goal_pw</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>2026-06-21T16:11:53</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>https://www.goal.com/en/news/world-cup-2026-eastern-time/blt57a4c6b10cc97d94</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>An all-you-need-to-know guide on how to watch every World Cup game broadcast live in the Eastern Time Zone
+The 2026 FIFA World Cup has completely tak</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>创历史，卡塔尔是世界杯史上第一支单场吃两红的亚足联球队</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>dongqiudi_team</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>2026-06-20 04:23</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>https://www.dongqiudi.com/articles/5950522.html</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Was Canada’s Win Over Qatar the Most One-Sided Game in World Cup History?</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>theanalyst_api</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>2026-06-19T15:12:21</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>https://theanalyst.com/articles/canada-win-over-qatar-one-sided-world-cup-2026/</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>It was wave after wave after wave, only Qatar’s second match at the 2026 FIFA World Cup was anything but a day at the beach.
+World Cup co-hosts Canad</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>World Cup 2026: Routes to the final</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>fifa</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>2026-06-19T12:00:00</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>https://www.fifa.com/en/articles/group-stage-permutations-qualify</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Find out what every team needs to qualify for the Round of 32 as group winners or runners-up, with information on Groups A-L, plus the tournament brac</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Canada 6-0 Qatar Stats: Hat-Trick Hero David Inspires Co-Hosts’ Historic First World Cup Win</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>theanalyst_api</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>2026-06-19T00:20:51</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>https://theanalyst.com/articles/canada-vs-qatar-stats-world-cup-2026-live/</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Co-hosts Canada put on a show in front of their fans in Vancouver, firing six goals past a nine-man Qatar to secure a 6-0 win; the biggest FIFA World </t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>盖村国家队战报：哲科卡蒂奇首发，十人波黑不敌瑞士</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>dongqiudi_team</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>2026-06-19 15:05</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>https://www.dongqiudi.com/articles/5948740.html</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>第33分钟染红，卡塔尔后卫霍马姆创世界杯2018年以来最快红牌</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>dongqiudi_team</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>2026-06-19 06:56</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>https://www.dongqiudi.com/articles/5947854.html</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Shocking Sunderland stat re-emerges, following Brian Brobbey masterclass</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>fourfourtwo</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Sat, 20 Jun 2026 20</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>https://www.fourfourtwo.com/competition/which-clubs-do-sunderland-have-more-players-than-at-the-2026-world-cup</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>In 2017/18, when Manchester City won the Premier League with 100 points, Sunderland were acclimating to Championship life.  The season prior, when Che</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Women’s T20 World Cup: West Indies defeat Sri Lanka by five wickets to stay unbeaten ahead of crunch England match</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>skysports</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Sat, 20 Jun 2026 14</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>https://www.skysports.com/cricket/news/12040/13556291/womens-t20-world-cup-west-indies-defeat-sri-lanka-by-five-wickets-to-stay-unbeaten-ahead-of-crunch-england-match</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Captain Hayley Matthews and Stafanie Taylor lead the way for West Indies, who join England on six points atop Group B after five-wicket win in low-sco</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>How far can the USA go at the 2026 World Cup? Hugely favourable route to semi-finals revealed</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>fourfourtwo</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Mon, 22 Jun 2026 08</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>https://www.fourfourtwo.com/team/how-far-can-the-usa-go-at-the-2026-world-cup-hugely-favourable-route-to-semi-finals-revealed</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">As the group stage of the 2026 FIFA World Cup nears its conclusion, the United States Men’s National Team (USMNT) have positioned themselves strongly </t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>New Zealand World Cup 2026: Fixtures, manager, squad depth and tactical analysis</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>squawka</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>7 hours ago</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>https://www.squawka.com/en/news/world-cup/new-zealand-world-cup-2026-fixtures-squad-analysis/</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>This summer marks New Zealand’s third appearance at a World Cup . They went unbeaten in their most recent appearance in 2010, but three draws wasn’t e</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>World Cup 2026 fixtures and results: Every fixture and kick-off time for the biggest World Cup ever</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>squawka</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>6 days ago</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>https://www.squawka.com/en/news/world-cup/world-cup-2026-fixtures-results/</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The 2026 World Cup is now well underway. Find the latest World Cup results and upcoming fixtures here.
+Get the latest World Cup Group A betting odds </t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Spain send statement with Saudi success</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>fifa</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>2026-06-21T18:00:00</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>https://www.fifa.com/en/articles/spain-saudi-arabia-highlights-match-report</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>This is a modal window.
+Oyarzabal and Yamal on target in dominant display as Luis de la Fuente's side showed their class with a comprehensive Group H</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Brazil vs Haiti Prediction: World Cup 2026 Match Preview</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>theanalyst_api</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>2026-06-19T21:55:38</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>https://theanalyst.com/articles/brazil-vs-haiti-prediction-world-cup-2026-match-preview/</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Brazil are out to secure a first win of their World Cup 2026 campaign when they face off against Haiti in Philadelphia. Look ahead to the Group C cont</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Group B: What did we learn in the second round?</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>sofascore</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>2026-06-19T13:54:58</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>https://www.sofascore.com/news/group-b-what-did-we-learn-in-the-second-round</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Canada and Switzerland seized control of Group B with statement wins, while Bosnia and Qatar now face a decisive fight for survival.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>世界杯B组前两轮积分榜：加拿大居首，下轮前二直接较量</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>dongqiudi_team</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>2026-06-19 10:27</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>https://www.dongqiudi.com/articles/5948244.html</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Uruguay vs Cape Verde Bet Builder: Uruguay to dominate in our 13/1 tip for tonight</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>squawka</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>13 hours ago</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>https://www.squawka.com/en/news/world-cup/uruguay-vs-cape-verde-bet-builder-21-06-2026/</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Uruguay will look to bring Cape Verde ‘s impressive unbeaten start to the 2026 World Cup to an end when the two nations meet in Group H at Hard Rock S</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E25"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="60" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="50" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>标题</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>来源</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>时间</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>URL</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>摘要</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>官方：阿根廷裁判法尔孔将执法世界杯捷克vs墨西哥</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>dongqiudi_team</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>2026-06-21 20:50</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>https://www.dongqiudi.com/articles/5955283.html</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>World Cup 2026 news and live updates - USA, Canada and Mexico latest including Trump, tickets and fans</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>skysports</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Sun, 21 Jun 2026 15</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>https://www.skysports.com/football/live-blog/12040/13509050/world-cup-2026-news-and-live-updates-usa-canada-and-mexico-latest-including-trump-tickets-and-fans</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Update World Cup 2026 news and live updates - USA, Canada and Mexico latest including Trump, tickets and fans Sunday 21 June 2026 15:14, UK Sorry, thi</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Giant Czech flag swallows World Cup staff member after national anthems</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>fourfourtwo</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Sun, 21 Jun 2026 05</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>https://www.fourfourtwo.com/competition/giant-czech-flag-swallows-world-cup-staff-member-after-national-anthems</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>We all loved playing parachute games at school, but the idea of being unexpectedly involved in one against your will is a terrifying prospect, as we'r</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>墨西哥前区长世界杯热舞，大方回应着装争议</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>dongqiudi_team</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>2026-06-22 11:19</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>https://www.dongqiudi.com/articles/5956722.html</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
           <t>World Cup on Fubo: Free trials, deals, offers, subscriptions, plans and more</t>
         </is>
       </c>
@@ -3187,6 +4453,1021 @@
         <is>
           <t xml:space="preserve">Written by RotoWire Staff
 Jurasek is likely out for the remainder of the World Cup after suffering a muscle injury in the pre-match training session </t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Bracketology: predict a path to World Cup victory</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>guardian</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Thu, 04 Jun 2026 10</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>https://www.theguardian.com/football/ng-interactive/2026/jun/04/bracketology-predict-a-path-to-world-cup-victory</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Click your way through the group stage and the knockouts to crown champion  Groups Touch and drag teams into predicted finish order  Third-place teams</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Australia’s Jackson Irvine has no sympathy for Paraguay after historic World Cup red card</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>guardian</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Sun, 21 Jun 2026 04</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>https://www.theguardian.com/football/2026/jun/21/australias-jackson-irvine-has-no-sympathy-for-paraguay-after-historic-world-cup-red-card</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Miguel Almirón sent off against Turkey for covering mouth  Socceroos face South Americans in crucial last Group D match  Socceroo Jackson Irvine has b</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Egypt World Cup 2026: Fixtures, manager, squad depth and tactical analysis</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>squawka</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>7 hours ago</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>https://www.squawka.com/en/news/world-cup/egypt-world-cup-2026-fixtures-players-analysis/</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Egypt are at the World Cup for the fourth time in their history. And they’ll be hoping to make it past the group stage for the first time.
+After a 1-</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>World Cup 2026 fixtures and results: Every fixture and kick-off time for the biggest World Cup ever</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>squawka</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>6 days ago</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>https://www.squawka.com/en/news/world-cup/world-cup-2026-fixtures-results/</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The 2026 World Cup is now well underway. Find the latest World Cup results and upcoming fixtures here.
+Get the latest World Cup Group A betting odds </t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Does it matter if Scotland lose and still make history?</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>bbc_sport</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>2026-06-21T21:39:43</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>https://www.bbc.com/sport/football/articles/ckg0exlle8yo?at_medium=RSS&amp;at_campaign=rss</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Steve Clarke and his squad are preparing for a potentially historic game  In a World Cup where the boffins with their big brainy heads and their super</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>How sweltering Scotland can handle World Cup heat</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>bbc_sport</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>2026-06-17T11:16:20</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>https://www.bbc.com/sport/football/articles/cx26geg0elgo?at_medium=RSS&amp;at_campaign=rss</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Scotland will face sweltering conditions in their final Group C match  Hydration breaks, ice jackets, cooling towels and isotonic drinks have been a f</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Belgium World Cup 2026: Fixtures, manager, squad depth &amp; tactical analysis</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>squawka</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>12 hours ago</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>https://www.squawka.com/en/news/world-cup/belgium-world-cup-2026-fixtures-squad-analysis-june-21/</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Belgium are back at the World Cup and desperate to give a much-improved account of themselves on the biggest stage. The Red Devils have got off to a s</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Argentina vs Austria: predictions, best bets, stats &amp; odds</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>squawka</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>1 hour ago</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>https://www.squawka.com/en/news/world-cup/argentina-vs-austria-predictions-betting-tips-22-06-26/</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">No previous meetings between these teams.
+No price boosts for this event.
+Bet Builder is not available yet.
+Betting markets are not available yet.
+</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>World Cup 2026 Group F: Latest table, fixtures and results</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>squawka</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>1 day ago</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>https://www.squawka.com/en/news/world-cup/world-cup-2026-group-f-latest-table-fixtures-and-results/</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Group F at World Cup 2026 looks to be one that has the potential for the biggest shock.
+The draw placed Netherlands into Group F alongside Japan and </t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E28"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="60" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="50" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>标题</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>来源</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>时间</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>URL</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>摘要</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>官方：阿根廷裁判特略将执法世界杯南非vs韩国</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>dongqiudi_team</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>2026-06-21 20:43</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>https://www.dongqiudi.com/articles/5955267.html</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>黄仁范：韩国0-1墨西哥但不会低落，战南非相信能赢</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>dongqiudi_team</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>2026-06-19 13:04</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>https://www.dongqiudi.com/articles/5948486.html</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>韩国前国脚李荣杓：日本队世界杯夺冠大概在1%左右</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>dongqiudi_team</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>2026-06-22 11:07</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>https://www.dongqiudi.com/articles/5956690.html</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>4-0突尼斯，日本终结连续5届世界杯小组赛第二轮不胜魔咒</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>dongqiudi</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>2026-06-22 07:41</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>https://www.dongqiudi.com/article/5956343</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>世界杯小组赛第二轮，日本对阵突尼斯，最终日本国家队4-0大胜突尼斯。
+据统计，日本本轮大胜后终结了连续5届世界杯小组赛第二轮不胜魔咒，自2006年世界杯以来，日本队在世界杯小组赛第二轮未尝胜绩，本届世界杯终于打破魔咒。
+日本世界杯小组赛第二轮战绩
+1998 法国世界杯
+次轮：日本 0-1 克罗地亚（</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>World Cup on Fubo: Free trials, deals, offers, subscriptions, plans and more</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>goal_pw</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>2026-06-21T18:22:43</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>https://www.goal.com/en/news/world-cup-2026-fubo/blt5f97df30090df47f</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GOAL explains how fans can stream live 2026 FIFA World Cup matches with Fubo
+The 2026 FIFA World Cup is officially underway, treating soccer fans to </t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Today's World Cup 2026 Kickoff Times: Complete Pacific Time (PT) Schedule</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>goal_pw</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>2026-06-21T17:04:43</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>https://www.goal.com/en/news/world-cup-2026-pacific-time-schedule/blt708391eb6f8f1517</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>An all-you-need-to-know guide on how to watch every World Cup game broadcast live in the Pacific Time Zone
+The 2026 FIFA World Cup has completely tak</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Today's World Cup 2026 Kickoff Times: Complete Mountain Time (MT) Schedule</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>goal_pw</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>2026-06-21T16:35:30</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>https://www.goal.com/en/news/world-cup-2026-mountain-time-schedule/blt2141270bc47c494f</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>An all-you-need-to-know guide on how to watch every World Cup game broadcast live in the Mountain Time Zone
+The 2026 FIFA World Cup has completely ta</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Today's World Cup 2026 Kickoff Times: Complete Eastern Time (ET) Schedule</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>goal_pw</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>2026-06-21T16:11:53</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>https://www.goal.com/en/news/world-cup-2026-eastern-time/blt57a4c6b10cc97d94</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>An all-you-need-to-know guide on how to watch every World Cup game broadcast live in the Eastern Time Zone
+The 2026 FIFA World Cup has completely tak</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Fastest World Cup to 100 goals in 68 years - are balls and breaks behind it?</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>bbc_sport</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>2026-06-20T23:46:26</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>https://www.bbc.com/sport/football/articles/cvglnkw1l93o?at_medium=RSS&amp;at_campaign=rss</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Messi, Mbappe and Vinicius Jr - the best World Cup goals from round one  The 2026 World Cup has become the fastest edition of the tournament to hit 10</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Most FIFA World Cup Appearances by a Player</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>theanalyst_api</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>2026-06-20T19:39:34</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>https://theanalyst.com/articles/most-world-cup-appearances-by-a-player/</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Here are the players who have combined longevity and excellence to record the most men’s FIFA World Cup appearances of all time.
+Lionel Messi: Argent</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Most Red Cards in World Cup History: Players, Teams and Incidents That Made History</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>theanalyst_api</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>2026-06-20T19:21:25</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>https://theanalyst.com/articles/most-red-cards-in-world-cup-history/</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">From Zinedine Zidane’s headbutt to Wayne Rooney’s stamp, discover which players and teams have received the most red cards in FIFA World Cup history.
+</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>韩足晚报（26.6.20）韩国便利店借世界杯营销，获成功</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>dongqiudi_team</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>2026-06-20 21:11</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>https://www.dongqiudi.com/articles/5951847.html</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>World Cup 2026: Routes to the final</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>fifa</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>2026-06-19T12:00:00</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>https://www.fifa.com/en/articles/group-stage-permutations-qualify</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Find out what every team needs to qualify for the Round of 32 as group winners or runners-up, with information on Groups A-L, plus the tournament brac</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Mexico Extend Incredible 100% World Cup Record Against South Korea</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>sofascore</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>2026-06-19T07:58:38</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>https://www.sofascore.com/news/mexico-extend-incredible-100-world-cup-record-against-south-korea</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Mexico beat South Korea in 1998, 2018 and 2026 at the FIFA World Cup. Key stats, shot maps and Sofascore Ratings explain how each game tilted Mexico’s</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>世界杯A组前两轮积分榜：墨西哥居首，韩国第二</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>dongqiudi_team</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>2026-06-19 11:00</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>https://www.dongqiudi.com/articles/5948291.html</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>武磊：感觉日本队每一个位置都没有短板，整体非常强大</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>dongqiudi</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>2026-06-22 08:32</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>https://www.dongqiudi.com/article/5956412</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>2026美加墨世界杯小组赛第2轮角逐，日本队4-0大胜突尼斯队。上海海港球员武磊在连线节目中表示：“感觉日本队每一个位置都没有短板，整体非常强大。”
+武磊说道：“我觉得现在日本队整体非常强大，每一个位置感觉都比较平均，好像没有哪一个位置稍弱一点。就像刚才说的，前锋位置上，不只是一个得分点，有很多得分</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>奇诚庸：孙兴慜的速度仍然很快，他在边路更有威胁</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>dongqiudi_team</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>2026-06-21 08:58</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>https://www.dongqiudi.com/articles/5954002.html</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>奥贝德：韩国不仅有孙兴慜，李刚仁也是一位非常出色的球员</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>dongqiudi_team</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>2026-06-20 07:53</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>https://www.dongqiudi.com/articles/5950944.html</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Bracketology: predict a path to World Cup victory</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>guardian</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Thu, 04 Jun 2026 10</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>https://www.theguardian.com/football/ng-interactive/2026/jun/04/bracketology-predict-a-path-to-world-cup-victory</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Click your way through the group stage and the knockouts to crown champion  Groups Touch and drag teams into predicted finish order  Third-place teams</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Australia’s Jackson Irvine has no sympathy for Paraguay after historic World Cup red card</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>guardian</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Sun, 21 Jun 2026 04</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>https://www.theguardian.com/football/2026/jun/21/australias-jackson-irvine-has-no-sympathy-for-paraguay-after-historic-world-cup-red-card</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Miguel Almirón sent off against Turkey for covering mouth  Socceroos face South Americans in crucial last Group D match  Socceroo Jackson Irvine has b</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Egypt World Cup 2026: Fixtures, manager, squad depth and tactical analysis</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>squawka</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>7 hours ago</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>https://www.squawka.com/en/news/world-cup/egypt-world-cup-2026-fixtures-players-analysis/</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Egypt are at the World Cup for the fourth time in their history. And they’ll be hoping to make it past the group stage for the first time.
+After a 1-</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>World Cup 2026 fixtures and results: Every fixture and kick-off time for the biggest World Cup ever</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>squawka</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>6 days ago</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>https://www.squawka.com/en/news/world-cup/world-cup-2026-fixtures-results/</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The 2026 World Cup is now well underway. Find the latest World Cup results and upcoming fixtures here.
+Get the latest World Cup Group A betting odds </t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Does it matter if Scotland lose and still make history?</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>bbc_sport</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>2026-06-21T21:39:43</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>https://www.bbc.com/sport/football/articles/ckg0exlle8yo?at_medium=RSS&amp;at_campaign=rss</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Steve Clarke and his squad are preparing for a potentially historic game  In a World Cup where the boffins with their big brainy heads and their super</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>How sweltering Scotland can handle World Cup heat</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>bbc_sport</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>2026-06-17T11:16:20</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>https://www.bbc.com/sport/football/articles/cx26geg0elgo?at_medium=RSS&amp;at_campaign=rss</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Scotland will face sweltering conditions in their final Group C match  Hydration breaks, ice jackets, cooling towels and isotonic drinks have been a f</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Belgium World Cup 2026: Fixtures, manager, squad depth &amp; tactical analysis</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>squawka</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>12 hours ago</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>https://www.squawka.com/en/news/world-cup/belgium-world-cup-2026-fixtures-squad-analysis-june-21/</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Belgium are back at the World Cup and desperate to give a much-improved account of themselves on the biggest stage. The Red Devils have got off to a s</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Argentina vs Austria: predictions, best bets, stats &amp; odds</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>squawka</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>1 hour ago</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>https://www.squawka.com/en/news/world-cup/argentina-vs-austria-predictions-betting-tips-22-06-26/</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">No previous meetings between these teams.
+No price boosts for this event.
+Bet Builder is not available yet.
+Betting markets are not available yet.
+</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>World Cup 2026 Group F: Latest table, fixtures and results</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>squawka</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>1 day ago</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>https://www.squawka.com/en/news/world-cup/world-cup-2026-group-f-latest-table-fixtures-and-results/</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Group F at World Cup 2026 looks to be one that has the potential for the biggest shock.
+The draw placed Netherlands into Group F alongside Japan and </t>
         </is>
       </c>
     </row>
